--- a/TestKit/TestKit/Q1/TC3_ReqResNotC/Header.xlsx
+++ b/TestKit/TestKit/Q1/TC3_ReqResNotC/Header.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7333B65-9BE8-40D9-8A5F-D3506041F24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FEF67B6-922F-4D39-8906-1B575F83B811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Testcase_Property" sheetId="1" r:id="rId1"/>
@@ -76,7 +76,7 @@
     <t>Grade_Content</t>
   </si>
   <si>
-    <t>Client/Server</t>
+    <t>Client</t>
   </si>
 </sst>
 </file>
@@ -87,7 +87,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -429,13 +429,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.1796875" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" customWidth="1"/>
+    <col min="1" max="1" width="21.19921875" customWidth="1"/>
+    <col min="2" max="2" width="15.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -443,7 +443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -451,7 +451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -459,7 +459,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -467,7 +467,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -475,7 +475,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
     </row>
   </sheetData>
@@ -486,9 +486,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE63C1B-9C74-4B75-BB3A-89FABA520B88}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>7</v>
       </c>
@@ -499,7 +499,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -508,7 +508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
         <v>12</v>
